--- a/output/yearly_total_coral_cover_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_73_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.269514091596716</v>
+        <v>1.257350237541099</v>
       </c>
       <c r="C3" t="n">
-        <v>4.611599706883761</v>
+        <v>4.578475539342474</v>
       </c>
       <c r="D3" t="n">
-        <v>6.070465217296548</v>
+        <v>6.126257939328895</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95157901577703</v>
+        <v>11.96208371621247</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.431374510771203</v>
+        <v>1.380930508621817</v>
       </c>
       <c r="C4" t="n">
-        <v>5.09301506515788</v>
+        <v>4.997668095341911</v>
       </c>
       <c r="D4" t="n">
-        <v>6.451659115767177</v>
+        <v>6.358304514205033</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97604869169626</v>
+        <v>12.73690311816876</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.641319785874495</v>
+        <v>1.546771856596929</v>
       </c>
       <c r="C5" t="n">
-        <v>5.690200816118276</v>
+        <v>5.510380942041373</v>
       </c>
       <c r="D5" t="n">
-        <v>6.837743501222166</v>
+        <v>6.79023606223696</v>
       </c>
       <c r="E5" t="n">
-        <v>14.16926410321494</v>
+        <v>13.84738886087526</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.869565299577588</v>
+        <v>1.73434159224918</v>
       </c>
       <c r="C6" t="n">
-        <v>6.446432100188107</v>
+        <v>6.15401344414455</v>
       </c>
       <c r="D6" t="n">
-        <v>7.187964869270022</v>
+        <v>7.242975980389763</v>
       </c>
       <c r="E6" t="n">
-        <v>15.50396226903572</v>
+        <v>15.13133101678349</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.119490473741796</v>
+        <v>1.941074758444404</v>
       </c>
       <c r="C7" t="n">
-        <v>7.332410485751469</v>
+        <v>6.938245445504623</v>
       </c>
       <c r="D7" t="n">
-        <v>7.622915945984072</v>
+        <v>7.650493857325631</v>
       </c>
       <c r="E7" t="n">
-        <v>17.07481690547734</v>
+        <v>16.52981406127466</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.304333549306298</v>
+        <v>1.167338877947175</v>
       </c>
       <c r="C8" t="n">
-        <v>5.039773186670414</v>
+        <v>4.661505155247524</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8886719824768</v>
+        <v>5.97369053418294</v>
       </c>
       <c r="E8" t="n">
-        <v>12.23277871845351</v>
+        <v>11.80253456737764</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.635694114829659</v>
+        <v>1.456732461791341</v>
       </c>
       <c r="C9" t="n">
-        <v>6.265028484975361</v>
+        <v>5.717764479821603</v>
       </c>
       <c r="D9" t="n">
-        <v>6.488422863340419</v>
+        <v>6.569585473121237</v>
       </c>
       <c r="E9" t="n">
-        <v>14.38914546314544</v>
+        <v>13.74408241473418</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.9928707778633</v>
+        <v>1.75870552056528</v>
       </c>
       <c r="C10" t="n">
-        <v>7.690014673481626</v>
+        <v>6.933368427984556</v>
       </c>
       <c r="D10" t="n">
-        <v>7.182651575265499</v>
+        <v>7.115042455119537</v>
       </c>
       <c r="E10" t="n">
-        <v>16.86553702661043</v>
+        <v>15.80711640366937</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.348752685154077</v>
+        <v>2.078795039384278</v>
       </c>
       <c r="C11" t="n">
-        <v>9.262559404586472</v>
+        <v>8.221385677338041</v>
       </c>
       <c r="D11" t="n">
-        <v>7.808997796725817</v>
+        <v>7.683890059172843</v>
       </c>
       <c r="E11" t="n">
-        <v>19.42030988646637</v>
+        <v>17.98407077589516</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.700028283127864</v>
+        <v>2.388541516147958</v>
       </c>
       <c r="C12" t="n">
-        <v>10.90037512827174</v>
+        <v>9.671409312811518</v>
       </c>
       <c r="D12" t="n">
-        <v>8.439377667903466</v>
+        <v>8.313835216258061</v>
       </c>
       <c r="E12" t="n">
-        <v>22.03978107930308</v>
+        <v>20.37378604521754</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.016016090781973</v>
+        <v>2.698866436510918</v>
       </c>
       <c r="C13" t="n">
-        <v>12.5437800129122</v>
+        <v>11.22452501842107</v>
       </c>
       <c r="D13" t="n">
-        <v>8.980920943124602</v>
+        <v>8.984677714475335</v>
       </c>
       <c r="E13" t="n">
-        <v>24.54071704681878</v>
+        <v>22.90806916940732</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.732931960151258</v>
+        <v>1.563855370525872</v>
       </c>
       <c r="C14" t="n">
-        <v>8.700640854116932</v>
+        <v>7.930243795640375</v>
       </c>
       <c r="D14" t="n">
-        <v>6.833562887657392</v>
+        <v>6.80149900763669</v>
       </c>
       <c r="E14" t="n">
-        <v>17.26713570192558</v>
+        <v>16.29559817380294</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.761127754217226</v>
+        <v>1.59837361980719</v>
       </c>
       <c r="C15" t="n">
-        <v>9.478224305788576</v>
+        <v>8.690666297441785</v>
       </c>
       <c r="D15" t="n">
-        <v>6.927820484742128</v>
+        <v>6.896473280545527</v>
       </c>
       <c r="E15" t="n">
-        <v>18.16717254474793</v>
+        <v>17.1855131977945</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.036449080396201</v>
+        <v>1.847727719208837</v>
       </c>
       <c r="C16" t="n">
-        <v>11.22066940119399</v>
+        <v>10.37042680193103</v>
       </c>
       <c r="D16" t="n">
-        <v>7.59330798354287</v>
+        <v>7.421227245942489</v>
       </c>
       <c r="E16" t="n">
-        <v>20.85042646513306</v>
+        <v>19.63938176708236</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.631419247532137</v>
+        <v>1.474938480952238</v>
       </c>
       <c r="C17" t="n">
-        <v>10.37234120995432</v>
+        <v>9.718389246678475</v>
       </c>
       <c r="D17" t="n">
-        <v>7.140486672436072</v>
+        <v>6.932611413538852</v>
       </c>
       <c r="E17" t="n">
-        <v>19.14424712992253</v>
+        <v>18.12593914116956</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.853726197681785</v>
+        <v>1.675293552434927</v>
       </c>
       <c r="C18" t="n">
-        <v>12.13826971044531</v>
+        <v>11.40486490546477</v>
       </c>
       <c r="D18" t="n">
-        <v>7.685022854073607</v>
+        <v>7.401425394747831</v>
       </c>
       <c r="E18" t="n">
-        <v>21.6770187622007</v>
+        <v>20.48158385264753</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.848837094114636</v>
+        <v>1.674949940738441</v>
       </c>
       <c r="C19" t="n">
-        <v>13.00124557743234</v>
+        <v>12.27262188377149</v>
       </c>
       <c r="D19" t="n">
-        <v>7.856121843969742</v>
+        <v>7.53522778935963</v>
       </c>
       <c r="E19" t="n">
-        <v>22.70620451551672</v>
+        <v>21.48279961386956</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.039836109975853</v>
+        <v>1.860883138445744</v>
       </c>
       <c r="C20" t="n">
-        <v>14.940246380705</v>
+        <v>14.16085651325755</v>
       </c>
       <c r="D20" t="n">
-        <v>8.328450481959925</v>
+        <v>7.97883048952355</v>
       </c>
       <c r="E20" t="n">
-        <v>25.30853297264078</v>
+        <v>24.00057014122684</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.20664646833567</v>
+        <v>1.10656710736475</v>
       </c>
       <c r="C21" t="n">
-        <v>10.97375985357591</v>
+        <v>10.42081009411298</v>
       </c>
       <c r="D21" t="n">
-        <v>7.000067298297651</v>
+        <v>6.665252061241318</v>
       </c>
       <c r="E21" t="n">
-        <v>19.18047362020923</v>
+        <v>18.19262926271905</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_73_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.257350237541099</v>
+        <v>1.264821337570417</v>
       </c>
       <c r="C3" t="n">
-        <v>4.578475539342474</v>
+        <v>4.671329237210137</v>
       </c>
       <c r="D3" t="n">
-        <v>6.126257939328895</v>
+        <v>6.098062145262927</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96208371621247</v>
+        <v>12.03421272004348</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.380930508621817</v>
+        <v>1.402271148636298</v>
       </c>
       <c r="C4" t="n">
-        <v>4.997668095341911</v>
+        <v>5.258954377736107</v>
       </c>
       <c r="D4" t="n">
-        <v>6.358304514205033</v>
+        <v>6.359255353883695</v>
       </c>
       <c r="E4" t="n">
-        <v>12.73690311816876</v>
+        <v>13.0204808802561</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.546771856596929</v>
+        <v>1.579916262860668</v>
       </c>
       <c r="C5" t="n">
-        <v>5.510380942041373</v>
+        <v>6.01232194247426</v>
       </c>
       <c r="D5" t="n">
-        <v>6.79023606223696</v>
+        <v>6.636480031000135</v>
       </c>
       <c r="E5" t="n">
-        <v>13.84738886087526</v>
+        <v>14.22871823633506</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.73434159224918</v>
+        <v>1.771695959728121</v>
       </c>
       <c r="C6" t="n">
-        <v>6.15401344414455</v>
+        <v>6.926205100385733</v>
       </c>
       <c r="D6" t="n">
-        <v>7.242975980389763</v>
+        <v>6.945178934206511</v>
       </c>
       <c r="E6" t="n">
-        <v>15.13133101678349</v>
+        <v>15.64307999432036</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.941074758444404</v>
+        <v>1.993247403989813</v>
       </c>
       <c r="C7" t="n">
-        <v>6.938245445504623</v>
+        <v>7.969105732716361</v>
       </c>
       <c r="D7" t="n">
-        <v>7.650493857325631</v>
+        <v>7.367785853434811</v>
       </c>
       <c r="E7" t="n">
-        <v>16.52981406127466</v>
+        <v>17.33013899014099</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.167338877947175</v>
+        <v>1.216509786174053</v>
       </c>
       <c r="C8" t="n">
-        <v>4.661505155247524</v>
+        <v>5.572286083975373</v>
       </c>
       <c r="D8" t="n">
-        <v>5.97369053418294</v>
+        <v>5.560454979364422</v>
       </c>
       <c r="E8" t="n">
-        <v>11.80253456737764</v>
+        <v>12.34925084951385</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.456732461791341</v>
+        <v>1.532514075234135</v>
       </c>
       <c r="C9" t="n">
-        <v>5.717764479821603</v>
+        <v>6.909235946357186</v>
       </c>
       <c r="D9" t="n">
-        <v>6.569585473121237</v>
+        <v>5.9965734053419</v>
       </c>
       <c r="E9" t="n">
-        <v>13.74408241473418</v>
+        <v>14.43832342693322</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.75870552056528</v>
+        <v>1.861411049491505</v>
       </c>
       <c r="C10" t="n">
-        <v>6.933368427984556</v>
+        <v>8.424724996231003</v>
       </c>
       <c r="D10" t="n">
-        <v>7.115042455119537</v>
+        <v>6.472400497332379</v>
       </c>
       <c r="E10" t="n">
-        <v>15.80711640366937</v>
+        <v>16.75853654305489</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.078795039384278</v>
+        <v>2.183302535866351</v>
       </c>
       <c r="C11" t="n">
-        <v>8.221385677338041</v>
+        <v>10.08275619883113</v>
       </c>
       <c r="D11" t="n">
-        <v>7.683890059172843</v>
+        <v>6.878353851794041</v>
       </c>
       <c r="E11" t="n">
-        <v>17.98407077589516</v>
+        <v>19.14441258649152</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.388541516147958</v>
+        <v>2.499903426843278</v>
       </c>
       <c r="C12" t="n">
-        <v>9.671409312811518</v>
+        <v>11.82801832233661</v>
       </c>
       <c r="D12" t="n">
-        <v>8.313835216258061</v>
+        <v>7.332977513789309</v>
       </c>
       <c r="E12" t="n">
-        <v>20.37378604521754</v>
+        <v>21.6608992629692</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.698866436510918</v>
+        <v>2.797942620784517</v>
       </c>
       <c r="C13" t="n">
-        <v>11.22452501842107</v>
+        <v>13.63649803292047</v>
       </c>
       <c r="D13" t="n">
-        <v>8.984677714475335</v>
+        <v>7.711433034304442</v>
       </c>
       <c r="E13" t="n">
-        <v>22.90806916940732</v>
+        <v>24.14587368800943</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.563855370525872</v>
+        <v>1.604509542958732</v>
       </c>
       <c r="C14" t="n">
-        <v>7.930243795640375</v>
+        <v>9.561515781016874</v>
       </c>
       <c r="D14" t="n">
-        <v>6.80149900763669</v>
+        <v>5.844992036866065</v>
       </c>
       <c r="E14" t="n">
-        <v>16.29559817380294</v>
+        <v>17.01101736084167</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.59837361980719</v>
+        <v>1.628532909281652</v>
       </c>
       <c r="C15" t="n">
-        <v>8.690666297441785</v>
+        <v>10.44073957250919</v>
       </c>
       <c r="D15" t="n">
-        <v>6.896473280545527</v>
+        <v>5.802619805950773</v>
       </c>
       <c r="E15" t="n">
-        <v>17.1855131977945</v>
+        <v>17.87189228774162</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.847727719208837</v>
+        <v>1.873950200389269</v>
       </c>
       <c r="C16" t="n">
-        <v>10.37042680193103</v>
+        <v>12.47193630268767</v>
       </c>
       <c r="D16" t="n">
-        <v>7.421227245942489</v>
+        <v>6.241205775345993</v>
       </c>
       <c r="E16" t="n">
-        <v>19.63938176708236</v>
+        <v>20.58709227842294</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.474938480952238</v>
+        <v>1.489252362480157</v>
       </c>
       <c r="C17" t="n">
-        <v>9.718389246678475</v>
+        <v>11.58746016097764</v>
       </c>
       <c r="D17" t="n">
-        <v>6.932611413538852</v>
+        <v>5.753031729409266</v>
       </c>
       <c r="E17" t="n">
-        <v>18.12593914116956</v>
+        <v>18.82974425286706</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.675293552434927</v>
+        <v>1.680251378341374</v>
       </c>
       <c r="C18" t="n">
-        <v>11.40486490546477</v>
+        <v>13.66575132852883</v>
       </c>
       <c r="D18" t="n">
-        <v>7.401425394747831</v>
+        <v>6.09079220957834</v>
       </c>
       <c r="E18" t="n">
-        <v>20.48158385264753</v>
+        <v>21.43679491644855</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.674949940738441</v>
+        <v>1.664199803376938</v>
       </c>
       <c r="C19" t="n">
-        <v>12.27262188377149</v>
+        <v>14.763629968711</v>
       </c>
       <c r="D19" t="n">
-        <v>7.53522778935963</v>
+        <v>6.131181310131053</v>
       </c>
       <c r="E19" t="n">
-        <v>21.48279961386956</v>
+        <v>22.55901108221899</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.860883138445744</v>
+        <v>1.829791188652248</v>
       </c>
       <c r="C20" t="n">
-        <v>14.16085651325755</v>
+        <v>16.99764595710983</v>
       </c>
       <c r="D20" t="n">
-        <v>7.97883048952355</v>
+        <v>6.444113390859724</v>
       </c>
       <c r="E20" t="n">
-        <v>24.00057014122684</v>
+        <v>25.2715505366218</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.10656710736475</v>
+        <v>1.076172198441269</v>
       </c>
       <c r="C21" t="n">
-        <v>10.42081009411298</v>
+        <v>12.52563790210997</v>
       </c>
       <c r="D21" t="n">
-        <v>6.665252061241318</v>
+        <v>5.333128418825863</v>
       </c>
       <c r="E21" t="n">
-        <v>18.19262926271905</v>
+        <v>18.93493851937711</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_73_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.264821337570417</v>
+        <v>2.606274604778665</v>
       </c>
       <c r="C3" t="n">
-        <v>4.671329237210137</v>
+        <v>7.780828781887559</v>
       </c>
       <c r="D3" t="n">
-        <v>6.098062145262927</v>
+        <v>8.127887048516765</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03421272004348</v>
+        <v>18.51499043518299</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.402271148636298</v>
+        <v>1.106486837645325</v>
       </c>
       <c r="C4" t="n">
-        <v>5.258954377736107</v>
+        <v>4.67527003699499</v>
       </c>
       <c r="D4" t="n">
-        <v>6.359255353883695</v>
+        <v>5.718346467691354</v>
       </c>
       <c r="E4" t="n">
-        <v>13.0204808802561</v>
+        <v>11.50010334233167</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.579916262860668</v>
+        <v>1.234878682174404</v>
       </c>
       <c r="C5" t="n">
-        <v>6.01232194247426</v>
+        <v>5.491245984779957</v>
       </c>
       <c r="D5" t="n">
-        <v>6.636480031000135</v>
+        <v>6.053475066531221</v>
       </c>
       <c r="E5" t="n">
-        <v>14.22871823633506</v>
+        <v>12.77959973348558</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.771695959728121</v>
+        <v>1.370720301859973</v>
       </c>
       <c r="C6" t="n">
-        <v>6.926205100385733</v>
+        <v>6.523998684510467</v>
       </c>
       <c r="D6" t="n">
-        <v>6.945178934206511</v>
+        <v>6.393796241389823</v>
       </c>
       <c r="E6" t="n">
-        <v>15.64307999432036</v>
+        <v>14.28851522776026</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.993247403989813</v>
+        <v>1.510187347489372</v>
       </c>
       <c r="C7" t="n">
-        <v>7.969105732716361</v>
+        <v>7.688293617570074</v>
       </c>
       <c r="D7" t="n">
-        <v>7.367785853434811</v>
+        <v>6.779552130845259</v>
       </c>
       <c r="E7" t="n">
-        <v>17.33013899014099</v>
+        <v>15.9780330959047</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.216509786174053</v>
+        <v>1.646620683531844</v>
       </c>
       <c r="C8" t="n">
-        <v>5.572286083975373</v>
+        <v>9.008542031494709</v>
       </c>
       <c r="D8" t="n">
-        <v>5.560454979364422</v>
+        <v>7.129712986766454</v>
       </c>
       <c r="E8" t="n">
-        <v>12.34925084951385</v>
+        <v>17.78487570179301</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.532514075234135</v>
+        <v>1.761307157875549</v>
       </c>
       <c r="C9" t="n">
-        <v>6.909235946357186</v>
+        <v>10.4329588138606</v>
       </c>
       <c r="D9" t="n">
-        <v>5.9965734053419</v>
+        <v>7.504706059956063</v>
       </c>
       <c r="E9" t="n">
-        <v>14.43832342693322</v>
+        <v>19.69897203169221</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.861411049491505</v>
+        <v>1.084124354845668</v>
       </c>
       <c r="C10" t="n">
-        <v>8.424724996231003</v>
+        <v>7.535767750596964</v>
       </c>
       <c r="D10" t="n">
-        <v>6.472400497332379</v>
+        <v>5.906685062600935</v>
       </c>
       <c r="E10" t="n">
-        <v>16.75853654305489</v>
+        <v>14.52657716804357</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.183302535866351</v>
+        <v>1.007440041666949</v>
       </c>
       <c r="C11" t="n">
-        <v>10.08275619883113</v>
+        <v>8.086263140799279</v>
       </c>
       <c r="D11" t="n">
-        <v>6.878353851794041</v>
+        <v>5.745786431351925</v>
       </c>
       <c r="E11" t="n">
-        <v>19.14441258649152</v>
+        <v>14.83948961381815</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.499903426843278</v>
+        <v>1.071823056111455</v>
       </c>
       <c r="C12" t="n">
-        <v>11.82801832233661</v>
+        <v>9.546033619720903</v>
       </c>
       <c r="D12" t="n">
-        <v>7.332977513789309</v>
+        <v>6.156775472780767</v>
       </c>
       <c r="E12" t="n">
-        <v>21.6608992629692</v>
+        <v>16.77463214861313</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.797942620784517</v>
+        <v>0.834318651500067</v>
       </c>
       <c r="C13" t="n">
-        <v>13.63649803292047</v>
+        <v>9.002940607208611</v>
       </c>
       <c r="D13" t="n">
-        <v>7.711433034304442</v>
+        <v>5.609215508214151</v>
       </c>
       <c r="E13" t="n">
-        <v>24.14587368800943</v>
+        <v>15.44647476692283</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.604509542958732</v>
+        <v>0.890631699815664</v>
       </c>
       <c r="C14" t="n">
-        <v>9.561515781016874</v>
+        <v>10.4907203481324</v>
       </c>
       <c r="D14" t="n">
-        <v>5.844992036866065</v>
+        <v>5.986805492744517</v>
       </c>
       <c r="E14" t="n">
-        <v>17.01101736084167</v>
+        <v>17.36815754069258</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.628532909281652</v>
+        <v>0.8533154695772428</v>
       </c>
       <c r="C15" t="n">
-        <v>10.44073957250919</v>
+        <v>11.26798964053868</v>
       </c>
       <c r="D15" t="n">
-        <v>5.802619805950773</v>
+        <v>6.038121445245498</v>
       </c>
       <c r="E15" t="n">
-        <v>17.87189228774162</v>
+        <v>18.15942655536142</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.873950200389269</v>
+        <v>0.9274766911560468</v>
       </c>
       <c r="C16" t="n">
-        <v>12.47193630268767</v>
+        <v>13.02648631090853</v>
       </c>
       <c r="D16" t="n">
-        <v>6.241205775345993</v>
+        <v>6.444260653015362</v>
       </c>
       <c r="E16" t="n">
-        <v>20.58709227842294</v>
+        <v>20.39822365507993</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.489252362480157</v>
+        <v>0.5549230723484672</v>
       </c>
       <c r="C17" t="n">
-        <v>11.58746016097764</v>
+        <v>9.624072744731484</v>
       </c>
       <c r="D17" t="n">
-        <v>5.753031729409266</v>
+        <v>5.365103941553182</v>
       </c>
       <c r="E17" t="n">
-        <v>18.82974425286706</v>
+        <v>15.54409975863313</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.680251378341374</v>
+        <v>0.4325089511059323</v>
       </c>
       <c r="C18" t="n">
-        <v>13.66575132852883</v>
+        <v>8.417416458918771</v>
       </c>
       <c r="D18" t="n">
-        <v>6.09079220957834</v>
+        <v>4.892245159802705</v>
       </c>
       <c r="E18" t="n">
-        <v>21.43679491644855</v>
+        <v>13.74217056982741</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.664199803376938</v>
+        <v>0.5062382036948677</v>
       </c>
       <c r="C19" t="n">
-        <v>14.763629968711</v>
+        <v>10.33465191558828</v>
       </c>
       <c r="D19" t="n">
-        <v>6.131181310131053</v>
+        <v>5.363336795685538</v>
       </c>
       <c r="E19" t="n">
-        <v>22.55901108221899</v>
+        <v>16.20422691496869</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.829791188652248</v>
+        <v>0.5733406592801373</v>
       </c>
       <c r="C20" t="n">
-        <v>16.99764595710983</v>
+        <v>12.41459241928261</v>
       </c>
       <c r="D20" t="n">
-        <v>6.444113390859724</v>
+        <v>5.878332188902287</v>
       </c>
       <c r="E20" t="n">
-        <v>25.2715505366218</v>
+        <v>18.86626526746504</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.076172198441269</v>
+        <v>0.6377040387705581</v>
       </c>
       <c r="C21" t="n">
-        <v>12.52563790210997</v>
+        <v>14.53837777544861</v>
       </c>
       <c r="D21" t="n">
-        <v>5.333128418825863</v>
+        <v>6.325263013783604</v>
       </c>
       <c r="E21" t="n">
-        <v>18.93493851937711</v>
+        <v>21.50134482800278</v>
       </c>
     </row>
   </sheetData>
